--- a/nr-update-reference-range/ig/StructureDefinition-mesures-observation-cholesterol-hdl.xlsx
+++ b/nr-update-reference-range/ig/StructureDefinition-mesures-observation-cholesterol-hdl.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T08:20:47+00:00</t>
+    <t>2026-03-19T08:22:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1713,7 +1713,7 @@
     <t>Observation.referenceRange.type</t>
   </si>
   <si>
-    <t>Reference range qualifier</t>
+    <t>Le type de référence permet d'indiquer s'il s'agit d'un intervalle de réfence ou d'un objectif cible.</t>
   </si>
   <si>
     <t>Codes to indicate the what part of the targeted reference population it applies to. For example, the normal or therapeutic range.</t>
@@ -10249,7 +10249,7 @@
         <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>82</v>
@@ -10371,7 +10371,7 @@
         <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>82</v>
